--- a/data/חכמים_ללא_מחקר.xlsx
+++ b/data/חכמים_ללא_מחקר.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="חכמים ללא מחקר" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'חכמים ללא מחקר'!$A$1:$K$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'חכמים ללא מחקר'!$A$1:$K$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1186,485 +1186,8 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>רבי יוסף חיון (רי״ח)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>ראשונים</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>מאה 15</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>ליסבון, פורטוגל</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>פרשנות מקרא/תיאולוגיה</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>תורה מן השמים, דיוק לשוני, ספר דברים, פרשנות סמנטית</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>מנהיג קהילת ליסבון ומורו של האברבנאל. פיתח פתרון לשאלת 'דברים מפי עצמו' ועיקרון שאין כפל עניין בתנ״ך.</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>משה ניסח נאומים, אך ה׳ הכתיב לו מילה במילה בעת כתיבת התורה; כל מילה במקרא ייחודית ואין 'נרדפות' סתמית.</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>דון יצחק אברבנאל; קנפנטון; המלבי״ם (הקדמה רעיונית)</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/5J3m8GmCr0dbgQl0IyUyW6</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>רבי ישראל אלנקוה</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>ראשונים</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>מאה 14</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>טולדו (ספרד)</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>מוסר/אגדה</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>מנורת המאור, פרעות קנ״א, כינוס מדרשים</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>מחבר 'מנורת המאור' מתוך כאב הדור והפיזור הרוחני. אסף מדרשים, אגדה וזוהר למסילת מוסר חיה ונגישה.</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>מוסר כ'מנגינה חיה': צדקה כתיקון והצלה; תפילה כעמידה של דלות; הבניית חיים דרך סיפורים ומשלים.</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>הרא״ש; יהדות ספרד לאחר 1391</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/7ong9XinXN1Na6aWhTzXME</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>רבנו חננאל בן חושיאל</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>ראשונים</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>מאה 11</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>קירואן (צפון אפריקה)</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>פירוש תלמוד/פסיקה</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>בהירות תלמוד, שיטתיות, שילוב ירושלמי בבבלי</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>גדול פוסקי קירואן והראשון שכתב פירוש שיטתי לתלמוד הבבלי. סיכם סוגיות בהירות והכשיר קרקע לרי״ף והרמב״ם.</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>מיפוי ים הסוגיות למסילה הלכתית: תמצות, בירור נוסח, ושילוב שיטתי של הירושלמי להכרעה.</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>רבנו ניסים; הרי״ף; הרמב״ם</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/580Us9ygui6IR3ypcVlNrx</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>594</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>רש"י (רבי שלמה יצחקי)</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>ראשונים</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1040–1105</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>טרואה</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>פרשנות המקרא, פרשנות התלמוד</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>גדול פרשני ישראל. פירושו לתורה ולתלמוד — בהיר, תמציתי וצמוד לפשט — פתח את שערי הלימוד לכל הדורות, ובלעדיו אין דף גמרא נלמד.</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>פשוטו של מקרא — פירוש שכל תלמיד יכול להיכנס בו</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>558</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>הבעל שם טוב (רבי ישראל בעש"ט)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>אחרונים</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>1698–1760</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>אוקראינה</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>חסידות, קבלה</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>מייסד תנועת החסידות. לימד שאין מקום פנוי ממנו, העמיד את הדבקות, השמחה ואהבת כל יהודי במרכז העבודה — ושינה את פני יהדות מזרח אירופה.</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>לית אתר פנוי מיניה — עבודת ה' בדבקות ובשמחה</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>הרב יוסף רוזין (הגאון הרוגצ'ובי)</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>אחרונים</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>1858–1936</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>רוגצ'וב/דווינסק</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>למדנות, רמב"ם, שיטת בריסק-חב"ד</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>צפנת פענח, רמב"ם, אחדות התורה, דווינסק, חב"ד</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>חד בדרא' שחי עם ש"ס ורמב"ם, קרא את הרמב"ם כמקשה אחת, וחיבר כלים פילוסופיים להבנת הלכה; כתבי היד ניצלו והונחו ליסוד מפעל הדפסה בדורות הבאים.</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>קריאת הרמב"ם כ'מערכת-על' המאחדת הלכה, אגדה ועיון מושגי תחת תורה אחת.</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>הרמב"ם; בעל האור שמח; אדמו"רי חב"ד (רש"ב, ריי"צ, הרבי)</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/4aUeMLx5QyMsdp0moTBcDu</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>חכם ציון חביב ברכה</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>מודרני</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>נפטר 2004 (י"ד בתשרי תשס"ה)</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>ירושלים (נחלאות)</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>קבלה</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>כוונות הרש"ש, תפילה, ענווה והסתרה, אהבת ישראל</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="3" t="inlineStr"/>
-      <c r="J22" s="3" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/54WDzXvPJL2lSljQw8ppji?si=axqFQefgQLCRM9oCzjRzxw&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>שושלת אבוחצירא</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>מודרני</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>המאה ה־19–20</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>מרוקו, ארץ ישראל</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>קבלה, הנהגה, פיוט</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>בבא סאלי, אעופה אשכונה, פיוט, גאולה</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>שושלת מקובלים שהובילה רוחנית את יהדות מרוקו. שילוב בין קדושה, ענווה ופיוט נשגב.</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>קדושה פרקטית מול פיוטי הגאולה. הנהגה רוחנית דרך חוויה ומסורת.</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>רבי ישראל אבוחצירא, רבי יצחק אבוחצירא</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/4zNV0OTiJsa1CUIm4xsy4e</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>תורת הקבלה – מבטו של אדולף פראנק (1843)</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>מודרני</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>המאה ה־19 (פרסום 1843)</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>צרפת / מסורת קבלה (ימי הביניים–צפת)</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>מחשבת ישראל (קבלה)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>אין־סוף וספירות, רע ותיקון, האר"י, זוהר, מחקר אקדמי</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>סקירת התפתחות הקבלה ממסורות קדומות עד הזוהר והאר"י, והצגת המהלך האקדמי של אדולף פראנק שראה בקבלה מערכת פילוסופית-דתית מתוחכמת. מדגיש מושגים כמו אין־סוף, ספירות, קליפות ותיקון.</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>הקבלה כמערכת מסבירה-כול: קוסמולוגיה, תיאודיציה ותיקון – וגם כמנוע התפתחות פנימי של מסורת.</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>אדולף פראנק; גרשם שלום (מובא בטקסט); האר"י; הזוהר</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/5qiFDQTROpb7v21w4imqIE?si=N2J3HnklTRW2Gm-BmT4SFA&amp;context=spotify%3Ashow%3A4nrvg1RLAoxg9C0vVYM8qv</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K24"/>
+  <autoFilter ref="A1:K15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/חכמים_ללא_מחקר.xlsx
+++ b/data/חכמים_ללא_מחקר.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="חכמים ללא מחקר" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'חכמים ללא מחקר'!$A$1:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'חכמים ללא מחקר'!$A$1:$K$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1186,8 +1186,179 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>הרב אליעזר יהודה וולדנברג (הציץ אליעזר)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1915–2006</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>ירושלים; ישראל</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>הלכה, רפואה וביו־אתיקה</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>ציץ אליעזר, רפואה והלכה, ביו־אתיקה, הפלות, הפריה חוץ־גופית, פונדקאות, השתלות, קביעת מוות, חולה הנוטה למות, עישון, הלכות מדינה</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>מגדולי הפוסקים בדור האחרון ומחלוצי הפסיקה הרפואית המודרנית. בשו״ת ״ציץ אליעזר״ בן 22 הכרכים בירר שאלות רפואיות וטכנולוגיות מתוך לימוד המציאות המדעית, וב״הלכות מדינה״ עסק בריבונות, צבא ומערכות ציבוריות במדינה יהודית.</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>ההלכה אינה נסוגה מפני מציאות חדשה: כדי לפסוק נכון יש להבין תחילה את העובדות המדעיות והחברתיות, ואז להחיל עליהן את עקרונות התורה מתוך אחריות לחיים, לאדם ולציבור.</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>הרב בן ציון מאיר חי עוזיאל, הרב יצחק אייזיק הלוי הרצוג, בית הדין הרבני הגדול, רופאי המרכז הרפואי שערי צדק</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/10vxjISIbCayZsVsHOxPXS?si=ybUiuUKNQ8eBppEJsXEqHQ&amp;utm_source=copy-link</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>הרב יהודה לייב הלוי אשלג (בעל הסולם)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1884–1954</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>פולין; ירושלים</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>קבלה והגות חברתית</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>בעל הסולם, פירוש הסולם, תלמוד עשר הספירות, הזוהר, האר״י, השוואת הצורה, רצון לקבל, רצון להשפיע, ערבות, הדור האחרון, האומה, בן־גוריון</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>מגדולי מפרשי הקבלה בעת החדשה. ב״תלמוד עשר הספירות״ סידר את כתבי האר״י לשיטה לימודית, וב״פירוש הסולם״ הנגיש את הזוהר. לצד זאת פיתח הגות חברתית שבמרכזה מעבר מן הרצון לקבל לעצמו אל אחריות, ערבות והשפעה.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>תיקון רוחני איננו נשאר בעולמות העליונים: שינוי הכוונה של היחיד אמור להקרין גם על מבנה החברה. אהבת הזולת, ערבות ואחריות הדדית הן בעיניו תרגום חברתי של רעיון ההשפעה הקבלי.</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>האר״י, הרמ״ק, הרב ברוך שלום אשלג (הרב״ש), דוד בן־גוריון, זלמן שזר</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/56ZfHwIuCVuWheqmgyawIj?si=3rkjd6YWTz6W7h1tqAVDJg&amp;utm_source=copy-link</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>הרב ישראל יצחק בזאנסון זצ״ל</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1944–2026</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>ניס; פריז; תל אביב</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>חסידות ברסלב, נפש ואמנות</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>ברסלב, רבי נחמן, שיר חדש, אומץ, נשמה נשימה, פאר הליקוטים, ציור, ניגון, התבודדות, תל אביב</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>רב, חסיד ברסלב, סופר, צייר ומלחין שחיבר בין עולם האמנות המודרנית לבין עבודת ה׳ ותורת רבי נחמן. הקים בתל אביב את קהילת ״שיר חדש״ ופיתח שפה של התמודדות נפשית, נשימה, יצירה והתבודדות.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>מסורת עמוקה יכולה לדבר אל האדם המודרני גם דרך צבע, צליל ונשימה; יצירה ורגישות נפשית אינן חלופה לעבודת ה׳ אלא יכולות להפוך לכלים של תפילה, צמיחה וחיבור.</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>רבי נחמן מברסלב, רבי לוי יצחק בנדר, רבי ישראל דב אודסר, ברברה רובין</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/5qT5Z7oVMNOWfC9CTUkR30?si=rnD76gn3TE2Nv8eV8ygNyA&amp;utm_source=copy-link</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K15"/>
+  <autoFilter ref="A1:K18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/חכמים_ללא_מחקר.xlsx
+++ b/data/חכמים_ללא_מחקר.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="חכמים ללא מחקר" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'חכמים ללא מחקר'!$A$1:$K$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'חכמים ללא מחקר'!$A$1:$K$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1186,179 +1186,8 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>הרב אליעזר יהודה וולדנברג (הציץ אליעזר)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>מודרני</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1915–2006</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>ירושלים; ישראל</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>הלכה, רפואה וביו־אתיקה</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>ציץ אליעזר, רפואה והלכה, ביו־אתיקה, הפלות, הפריה חוץ־גופית, פונדקאות, השתלות, קביעת מוות, חולה הנוטה למות, עישון, הלכות מדינה</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>מגדולי הפוסקים בדור האחרון ומחלוצי הפסיקה הרפואית המודרנית. בשו״ת ״ציץ אליעזר״ בן 22 הכרכים בירר שאלות רפואיות וטכנולוגיות מתוך לימוד המציאות המדעית, וב״הלכות מדינה״ עסק בריבונות, צבא ומערכות ציבוריות במדינה יהודית.</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>ההלכה אינה נסוגה מפני מציאות חדשה: כדי לפסוק נכון יש להבין תחילה את העובדות המדעיות והחברתיות, ואז להחיל עליהן את עקרונות התורה מתוך אחריות לחיים, לאדם ולציבור.</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>הרב בן ציון מאיר חי עוזיאל, הרב יצחק אייזיק הלוי הרצוג, בית הדין הרבני הגדול, רופאי המרכז הרפואי שערי צדק</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/10vxjISIbCayZsVsHOxPXS?si=ybUiuUKNQ8eBppEJsXEqHQ&amp;utm_source=copy-link</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>הרב יהודה לייב הלוי אשלג (בעל הסולם)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>מודרני</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>1884–1954</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>פולין; ירושלים</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>קבלה והגות חברתית</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>בעל הסולם, פירוש הסולם, תלמוד עשר הספירות, הזוהר, האר״י, השוואת הצורה, רצון לקבל, רצון להשפיע, ערבות, הדור האחרון, האומה, בן־גוריון</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>מגדולי מפרשי הקבלה בעת החדשה. ב״תלמוד עשר הספירות״ סידר את כתבי האר״י לשיטה לימודית, וב״פירוש הסולם״ הנגיש את הזוהר. לצד זאת פיתח הגות חברתית שבמרכזה מעבר מן הרצון לקבל לעצמו אל אחריות, ערבות והשפעה.</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>תיקון רוחני איננו נשאר בעולמות העליונים: שינוי הכוונה של היחיד אמור להקרין גם על מבנה החברה. אהבת הזולת, ערבות ואחריות הדדית הן בעיניו תרגום חברתי של רעיון ההשפעה הקבלי.</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>האר״י, הרמ״ק, הרב ברוך שלום אשלג (הרב״ש), דוד בן־גוריון, זלמן שזר</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/56ZfHwIuCVuWheqmgyawIj?si=3rkjd6YWTz6W7h1tqAVDJg&amp;utm_source=copy-link</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>הרב ישראל יצחק בזאנסון זצ״ל</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>מודרני</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>1944–2026</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>ניס; פריז; תל אביב</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>חסידות ברסלב, נפש ואמנות</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>ברסלב, רבי נחמן, שיר חדש, אומץ, נשמה נשימה, פאר הליקוטים, ציור, ניגון, התבודדות, תל אביב</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>רב, חסיד ברסלב, סופר, צייר ומלחין שחיבר בין עולם האמנות המודרנית לבין עבודת ה׳ ותורת רבי נחמן. הקים בתל אביב את קהילת ״שיר חדש״ ופיתח שפה של התמודדות נפשית, נשימה, יצירה והתבודדות.</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>מסורת עמוקה יכולה לדבר אל האדם המודרני גם דרך צבע, צליל ונשימה; יצירה ורגישות נפשית אינן חלופה לעבודת ה׳ אלא יכולות להפוך לכלים של תפילה, צמיחה וחיבור.</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>רבי נחמן מברסלב, רבי לוי יצחק בנדר, רבי ישראל דב אודסר, ברברה רובין</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>https://open.spotify.com/episode/5qT5Z7oVMNOWfC9CTUkR30?si=rnD76gn3TE2Nv8eV8ygNyA&amp;utm_source=copy-link</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K18"/>
+  <autoFilter ref="A1:K15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>